--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>89411880</v>
       </c>
       <c r="B13" t="n">
-        <v>101794</v>
+        <v>102095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,23 +2013,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222929</v>
+        <v>224938</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backruta</t>
+          <t>Vanlig backruta</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thalictrum simplex</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Thalictrum simplex subsp. simplex</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>58</t>
@@ -2040,11 +2036,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>89411880</v>
       </c>
       <c r="B13" t="n">
-        <v>102095</v>
+        <v>102098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>89411880</v>
       </c>
       <c r="B13" t="n">
-        <v>102098</v>
+        <v>102104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>89411880</v>
       </c>
       <c r="B13" t="n">
-        <v>102104</v>
+        <v>102116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>89411880</v>
       </c>
       <c r="B13" t="n">
-        <v>102116</v>
+        <v>102117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>89411880</v>
       </c>
       <c r="B13" t="n">
-        <v>102117</v>
+        <v>102120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>89411880</v>
       </c>
       <c r="B13" t="n">
-        <v>102120</v>
+        <v>102124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
